--- a/Result/profitability/6474.xlsx
+++ b/Result/profitability/6474.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM32"/>
+  <dimension ref="A1:AM33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4494,6 +4494,133 @@
         <v>115.1</v>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>6474</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>1196</v>
+      </c>
+      <c r="D33" t="n">
+        <v>945</v>
+      </c>
+      <c r="E33" t="n">
+        <v>251</v>
+      </c>
+      <c r="F33" t="n">
+        <v>20.98</v>
+      </c>
+      <c r="G33" t="n">
+        <v>71</v>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>5.91%</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
+        <v>3</v>
+      </c>
+      <c r="J33" t="n">
+        <v>73</v>
+      </c>
+      <c r="K33" t="n">
+        <v>61</v>
+      </c>
+      <c r="L33" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0.8925</v>
+      </c>
+      <c r="N33" t="n">
+        <v>21.6925</v>
+      </c>
+      <c r="O33" t="n">
+        <v>1</v>
+      </c>
+      <c r="P33" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>1</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" t="n">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>0</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
+      </c>
+      <c r="V33" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W33" t="n">
+        <v>0.2499999999999999</v>
+      </c>
+      <c r="X33" t="n">
+        <v>0.2777777777777777</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>-0.8299999999999983</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>-0.03805593764328286</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>0.2799999999999999</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>0.3218390804597699</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>-1.419999999999998</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>-0.06339285714285703</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK33" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>115.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
